--- a/EIBE_CS_SKU정보_HUAWEI_260109.xlsx
+++ b/EIBE_CS_SKU정보_HUAWEI_260109.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\지윤환\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\지윤환\Desktop\DEVELOP_web\eibe_cs_mock_up\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C990D0BF-5997-4FF6-B50C-E37559DEB565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE874EBB-ACE7-4E69-8695-4FDFBCC852F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -367,22 +367,27 @@
     <t>(본품) HUAWEI 프리버드 SE 4 ANC (Black)</t>
   </si>
   <si>
-    <t>HUAWEI FIT4 퀵링크 워치밴드 (Black)</t>
-  </si>
-  <si>
-    <t>HUAWEI FIT4 퀵링크 워치밴드 (White)</t>
-  </si>
-  <si>
-    <t>HUAWEI FIT4 퀵링크 워치밴드 (Purple)</t>
-  </si>
-  <si>
-    <t>HUAWEI FIT4Pro 퀵링크 워치밴드 (Blue)</t>
-  </si>
-  <si>
-    <t>HUAWEI FIT4Pro 퀵링크 Nylon 밴드 (Green)</t>
-  </si>
-  <si>
     <t>(본품) HUAWEI Scale 3</t>
+  </si>
+  <si>
+    <t>HUAWEI FIT4 퀵링크 나일론 워치밴드 (Black)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HUAWEI FIT4 퀵링크 나일론 워치밴드 (White)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HUAWEI FIT4 퀵링크 나일론 워치밴드 (Purple)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HUAWEI FIT 4 Pro 퀵링크 워치밴드 (Blue)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HUAWEI FIT 4 Pro 퀵링크 나일론 워치밴드 (Green)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -998,7 +1003,7 @@
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>71</v>
@@ -1013,7 +1018,7 @@
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>72</v>
@@ -1028,7 +1033,7 @@
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>73</v>
@@ -1043,7 +1048,7 @@
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>74</v>
@@ -1058,7 +1063,7 @@
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F15" s="11"/>
     </row>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F16" s="11"/>
     </row>
